--- a/programs/assembly/tage_test.xlsx
+++ b/programs/assembly/tage_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emerald\zaqal\programs\assembly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B3B270-3112-4ADC-9404-6475607F4610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1515A9CF-4FC9-4D5E-B0CD-B95D46F1719C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29415" yWindow="-2505" windowWidth="6345" windowHeight="8505" xr2:uid="{B74E0A7A-CC7C-4599-9383-8688FA3B4D88}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B74E0A7A-CC7C-4599-9383-8688FA3B4D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>jal x0, 24</t>
   </si>
@@ -139,13 +139,43 @@
   </si>
   <si>
     <t>x40</t>
+  </si>
+  <si>
+    <t>00a00093</t>
+  </si>
+  <si>
+    <t>        "h000200e7".U, // 0x34: jalr x1, x4, 0    10|x1 = 0x38|(Dynamic indirect jump to Target A or B)</t>
+  </si>
+  <si>
+    <t>        "hfff08093".U, // 0x38: addi x1, x1, -1   (Decrement outer loop counter)</t>
+  </si>
+  <si>
+    <t>        "hfc0096e3".U, // 0x3c: bne x1, x0, -52   13||(If x1 != 0, branch to Loop Start at 0x08)</t>
+  </si>
+  <si>
+    <t>        "h06300613"</t>
+  </si>
+  <si>
+    <t>0032f713</t>
+  </si>
+  <si>
+    <t>0140026f</t>
+  </si>
+  <si>
+    <t>00a00793</t>
+  </si>
+  <si>
+    <t>0180006f</t>
+  </si>
+  <si>
+    <t>0100006f</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +196,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -209,10 +245,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,146 +566,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC81516-6F18-46D2-9BCA-77E7B9AB92B0}">
-  <dimension ref="A2:B18"/>
+  <dimension ref="A2:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D3" s="3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D4" s="3">
+        <v>628293</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D5" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D6" s="3">
+        <v>70463</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D7" s="3">
+        <v>100793</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D8" s="3">
+        <v>271893</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D9" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D10" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D11" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D12" s="3">
+        <v>1400793</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D13" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D14" s="3">
+        <v>1120233</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D15" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D17" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/programs/assembly/tage_test.xlsx
+++ b/programs/assembly/tage_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emerald\zaqal\programs\assembly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1515A9CF-4FC9-4D5E-B0CD-B95D46F1719C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0926A3-0C56-4228-8FDC-72B31A7AF907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B74E0A7A-CC7C-4599-9383-8688FA3B4D88}"/>
+    <workbookView xWindow="34230" yWindow="6960" windowWidth="4620" windowHeight="9870" xr2:uid="{B74E0A7A-CC7C-4599-9383-8688FA3B4D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>jal x0, 24</t>
   </si>
@@ -144,18 +144,6 @@
     <t>00a00093</t>
   </si>
   <si>
-    <t>        "h000200e7".U, // 0x34: jalr x1, x4, 0    10|x1 = 0x38|(Dynamic indirect jump to Target A or B)</t>
-  </si>
-  <si>
-    <t>        "hfff08093".U, // 0x38: addi x1, x1, -1   (Decrement outer loop counter)</t>
-  </si>
-  <si>
-    <t>        "hfc0096e3".U, // 0x3c: bne x1, x0, -52   13||(If x1 != 0, branch to Loop Start at 0x08)</t>
-  </si>
-  <si>
-    <t>        "h06300613"</t>
-  </si>
-  <si>
     <t>0032f713</t>
   </si>
   <si>
@@ -169,6 +157,15 @@
   </si>
   <si>
     <t>0100006f</t>
+  </si>
+  <si>
+    <t>fc0096e3</t>
+  </si>
+  <si>
+    <t>fff08093</t>
+  </si>
+  <si>
+    <t>"000200e7"</t>
   </si>
 </sst>
 </file>
@@ -613,7 +610,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -657,7 +654,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -668,7 +665,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -679,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -701,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -723,7 +720,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -734,7 +731,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -745,7 +742,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -755,8 +752,8 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>38</v>
+      <c r="D18" s="3">
+        <v>6300613</v>
       </c>
     </row>
   </sheetData>
